--- a/Istruzioni.xlsx
+++ b/Istruzioni.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fetspa-my.sharepoint.com/personal/bruno_sanzi_fiamm_com/Documents/Documenti/GitHub/Manutenzione/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\Manutenzione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC1048A0215E60145BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3D2862E-B9AE-4039-8C2C-903DA1F11810}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1201067F-4949-4DF1-B422-D5BE0D7AC693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Scaricare da evidon dati del trimestre da analizzare</t>
   </si>
@@ -195,17 +195,718 @@
     <t>FUNZIONAMENTO PROGRAMMA</t>
   </si>
   <si>
-    <t>sheet per sheet</t>
-  </si>
-  <si>
     <t>Quali sheet cancellare (se cambi linea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2° sheet --&gt; </t>
+  </si>
+  <si>
+    <t>cambi_prod_L1</t>
+  </si>
+  <si>
+    <t>Se il cambio produzione è presente in due giorni consecutivi, i relativi minuti di fermo vengono accorpati e riportati come un unico evento, indicando la data del primo giorno e i minuti complessivi dei due.</t>
+  </si>
+  <si>
+    <t>Vengono escluse i fermi non rilevanti (es. pausa caffè, pausa pranzo).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inoltre, se una </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>macchina ha avuto più di un fermo nello stesso giorno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, i relativi minuti vengono </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>accorpati</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in un'unica voce. </t>
+    </r>
+  </si>
+  <si>
+    <t>I dati sono ordinati per tempo totale di fermo decrescente, così da evidenziare le macchine più critiche.</t>
+  </si>
+  <si>
+    <t>Le analisi successive si basano sui dati del 3°sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contiene l’analisi della RUL (Remaining Useful Life) per la macchina specificata.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">il numero di giorni trascorsi dal fermo precedente (colonna </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minuti di fermo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> registrati in quella data, </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Riporta, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data e ora</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in cui si è verificato un fermo,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>variabilità</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> della RUL.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">l’andamento della </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RUL nel tempo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (linea blu),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minuti di fermo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> per ciascun giorno (barre rosse),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">e i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minuti dovuti a cambi produzione</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (barre verdi).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1° sheet  --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">estrazione di </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>evidon</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3°sheet --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fermi_linea_1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4°sheet --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>analisi_fermi_per_macchina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5°sheet --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>analisi_fermi_per_pezzo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6°sheet --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>analisi_fermi_per_classe</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7°sheet --&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RUL_nome_macchina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">8°sheet--&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cambio produzione_RUL_linea_macchina</t>
+    </r>
+  </si>
+  <si>
+    <t>In questo sheet vengono eliminati tutti i fermi relativi a : assemblea, blackout, fermo programmato, fermo pulizia,  pausa caffè, pausa pranzo,  pulizia fine turno,  rps).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Riporta la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minuti di fermo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dei cambi produzione della linea scelta.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Riporta gli stessi dati del 1°sheet ma filtrati. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mostra, per ciascuna macchina, il </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>numero totale di fermi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, il </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tempo totale di fermo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, la </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>frequenza media dei guasti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e l'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MTBF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mostra le stesse informazioni del 4°sheet ma suddivise per coppia</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> macchina–pezzo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, permettendo di identificare quali pezzi causano più problemi su ciascuna macchina.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Riporta la stessa analisi del 4°sheet ma suddivisa per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>macchina</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pezzo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>classe di guasto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>I dati sono ordinati cronologicamente e permettono di valutare ogni quanti giorni si verificano i guasti sulla macchina selezionata.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unisce le date dei fermi per </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cambio produzione</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con quelle delle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RUL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> della macchina analizzata.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Viene generato un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>grafico</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in formato </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, che mostra:</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,13 +951,55 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -271,8 +1014,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -553,67 +1303,239 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:U58"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="9.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5">
       <c r="B9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5">
       <c r="B11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5">
       <c r="B12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
       <c r="B13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="16" spans="2:5" ht="18">
+      <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="2:21" ht="18">
       <c r="B17" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" ht="15.6">
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21">
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21">
+      <c r="C21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+    </row>
+    <row r="23" spans="2:21" ht="15.6">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21">
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21">
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21">
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21">
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" ht="15.6">
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="15.6">
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="15.6">
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="15.6">
+      <c r="B42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="C43" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="C46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" ht="15.6">
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="C52" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" ht="15.6">
+      <c r="B55" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Istruzioni.xlsx
+++ b/Istruzioni.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\GitHub\Manutenzione\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fetspa-my.sharepoint.com/personal/bruno_sanzi_fiamm_com/Documents/Documenti/GitHub/Manutenzione/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1201067F-4949-4DF1-B422-D5BE0D7AC693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{1201067F-4949-4DF1-B422-D5BE0D7AC693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBCA95A6-908D-4FB5-9F35-C718DBCBE7FE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Scaricare da evidon dati del trimestre da analizzare</t>
   </si>
@@ -183,19 +183,7 @@
     </r>
   </si>
   <si>
-    <t>NOTA Aggiustamento / Filtro</t>
-  </si>
-  <si>
-    <t>Cambi produzione accorpa ..</t>
-  </si>
-  <si>
-    <t>Pausa caffèelimina ..</t>
-  </si>
-  <si>
     <t>FUNZIONAMENTO PROGRAMMA</t>
-  </si>
-  <si>
-    <t>Quali sheet cancellare (se cambi linea)</t>
   </si>
   <si>
     <t xml:space="preserve">2° sheet --&gt; </t>
@@ -906,7 +894,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1014,9 +1002,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1303,239 +1290,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U58"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B1:E54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
-      <c r="B11" t="s">
+    <row r="12" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="18">
-      <c r="B16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:21" ht="18">
-      <c r="B17" t="s">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:21" ht="15.6">
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="2:21">
-      <c r="C20" t="s">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:21">
-      <c r="C21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-    </row>
-    <row r="23" spans="2:21" ht="15.6">
-      <c r="B23" t="s">
+    <row r="38" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:21">
-      <c r="C24" t="s">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:21">
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="2:21">
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:21">
-      <c r="C28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21">
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" ht="15.6">
-      <c r="B32" t="s">
+    <row r="47" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="2:3">
-      <c r="C33" t="s">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="2:3">
-      <c r="C34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="15.6">
-      <c r="B36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="C37" t="s">
+    <row r="51" spans="2:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="15.6">
-      <c r="B39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3">
-      <c r="C40" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" ht="15.6">
-      <c r="B42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3">
-      <c r="C43" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3">
-      <c r="C44" t="s">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3">
-      <c r="C45" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3">
-      <c r="C46" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3">
-      <c r="C47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3">
-      <c r="C49" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" ht="15.6">
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3">
-      <c r="C52" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" ht="15.6">
-      <c r="B55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3">
-      <c r="B56" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3">
-      <c r="B57" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3">
-      <c r="B58" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
